--- a/data/trans_bre/P16A03-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A03-Edad-trans_bre.xlsx
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,77</t>
+          <t>1,78; 5,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,03</t>
+          <t>-0,23; 2,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,82</t>
+          <t>1,29; 4,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 5,61</t>
+          <t>-0,33; 4,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>134,47; —</t>
+          <t>123,74; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-46,24; 784,8</t>
+          <t>-35,66; 999,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,92</t>
+          <t>2,01; 5,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,47</t>
+          <t>2,04; 6,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,19</t>
+          <t>0,19; 3,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,49</t>
+          <t>0,55; 4,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>169,2; 1572,93</t>
+          <t>146,69; 1708,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,47; 862,84</t>
+          <t>67,9; 790,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 651,83</t>
+          <t>-3,38; 602,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-37,62; 6762,1</t>
+          <t>-28,41; 6826,37</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,76</t>
+          <t>-0,66; 2,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,96</t>
+          <t>3,36; 7,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,18</t>
+          <t>2,0; 5,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 2,85</t>
+          <t>-0,22; 2,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,21; 205,76</t>
+          <t>-26,29; 203,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>234,4; 2397,08</t>
+          <t>245,66; 2150,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>137,4; 2473,52</t>
+          <t>129,68; 2393,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-21,17; 528,61</t>
+          <t>-20,73; 487,24</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,8</t>
+          <t>0,28; 4,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,85</t>
+          <t>2,0; 5,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,99</t>
+          <t>1,38; 5,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,43</t>
+          <t>1,67; 5,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,19; 506,11</t>
+          <t>2,77; 541,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,23; 1724,0</t>
+          <t>98,82; 1312,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,85; 1020,49</t>
+          <t>55,81; 925,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>60,12; 742,9</t>
+          <t>59,22; 751,01</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 6,66</t>
+          <t>0,43; 6,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 7,95</t>
+          <t>3,13; 8,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 4,43</t>
+          <t>0,33; 4,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,2</t>
+          <t>0,87; 5,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 352,48</t>
+          <t>-0,94; 349,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>125,81; 3315,39</t>
+          <t>172,74; 3730,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 565,08</t>
+          <t>-3,88; 544,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,31; 194,38</t>
+          <t>15,99; 183,11</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,23; 10,8</t>
+          <t>2,65; 10,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,41</t>
+          <t>1,19; 8,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 6,83</t>
+          <t>1,32; 6,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 3,82</t>
+          <t>-2,6; 3,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,81; 395,27</t>
+          <t>29,59; 426,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,28; 468,61</t>
+          <t>8,63; 438,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,0; 635,21</t>
+          <t>29,5; 718,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,13; 131,03</t>
+          <t>-52,66; 142,51</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 4,26</t>
+          <t>-6,62; 4,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,13; 13,27</t>
+          <t>3,24; 12,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 6,1</t>
+          <t>-1,3; 6,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,63; 9,88</t>
+          <t>4,58; 10,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-55,59; 88,14</t>
+          <t>-56,48; 89,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,42; 851,77</t>
+          <t>35,87; 883,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-25,88; 215,18</t>
+          <t>-27,59; 220,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>81,66; 420,95</t>
+          <t>81,23; 434,09</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,99</t>
+          <t>2,15; 4,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,8; 5,62</t>
+          <t>3,78; 5,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,65</t>
+          <t>2,0; 3,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,78</t>
+          <t>1,98; 3,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>81,59; 222,67</t>
+          <t>79,37; 217,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>221,47; 535,8</t>
+          <t>216,49; 535,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>130,28; 361,75</t>
+          <t>127,53; 354,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>84,72; 237,71</t>
+          <t>87,24; 239,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A03-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A03-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,7</t>
+          <t>2,01</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>375,94%</t>
+          <t>494,18%</t>
         </is>
       </c>
     </row>
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,48</t>
+          <t>1,83; 5,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 2,85</t>
+          <t>-0,19; 3,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,82</t>
+          <t>1,26; 4,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 4,89</t>
+          <t>0,24; 5,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>123,74; —</t>
+          <t>127,88; 2642,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,66; 999,59</t>
+          <t>-40,65; 882,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,25</t>
+          <t>1,88</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>504,75%</t>
+          <t>153,82%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,84</t>
+          <t>2,14; 5,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 6,24</t>
+          <t>2,14; 6,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,11</t>
+          <t>0,31; 3,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,27</t>
+          <t>-0,16; 3,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>146,69; 1708,27</t>
+          <t>139,62; 1519,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,9; 790,82</t>
+          <t>80,48; 929,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 602,19</t>
+          <t>6,0; 788,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,41; 6826,37</t>
+          <t>-32,53; —</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>1,68</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>113,33%</t>
+          <t>154,73%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,78</t>
+          <t>-0,81; 2,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 7,26</t>
+          <t>3,33; 7,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,51</t>
+          <t>2,02; 5,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 2,82</t>
+          <t>0,37; 3,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-26,29; 203,84</t>
+          <t>-30,71; 222,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>245,66; 2150,46</t>
+          <t>207,19; 2029,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>129,68; 2393,21</t>
+          <t>145,74; 2758,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-20,73; 487,24</t>
+          <t>-1,86; 592,42</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>2,87</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>211,48%</t>
+          <t>127,61%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 4,54</t>
+          <t>0,37; 4,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,95</t>
+          <t>1,79; 5,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 5,01</t>
+          <t>1,26; 4,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,28</t>
+          <t>1,1; 4,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 541,88</t>
+          <t>3,51; 590,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,82; 1312,5</t>
+          <t>102,72; 1443,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,81; 925,93</t>
+          <t>40,66; 914,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>59,22; 751,01</t>
+          <t>29,52; 346,96</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,11</t>
+          <t>3,47</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 6,76</t>
+          <t>0,44; 6,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,13; 8,0</t>
+          <t>3,11; 7,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,66</t>
+          <t>0,11; 4,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,17</t>
+          <t>0,73; 5,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 349,01</t>
+          <t>2,4; 353,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>172,74; 3730,77</t>
+          <t>127,07; 3106,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 544,43</t>
+          <t>-12,11; 560,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,99; 183,11</t>
+          <t>16,53; 197,69</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>3,32</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>100,17%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,65; 10,48</t>
+          <t>2,37; 10,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 8,64</t>
+          <t>0,98; 8,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,69</t>
+          <t>0,95; 6,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 3,81</t>
+          <t>1,03; 5,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,59; 426,67</t>
+          <t>31,1; 394,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,63; 438,29</t>
+          <t>-0,09; 460,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,5; 718,08</t>
+          <t>14,78; 713,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-52,66; 142,51</t>
+          <t>20,08; 241,91</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,31</t>
+          <t>6,72</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>198,49%</t>
+          <t>171,24%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 4,1</t>
+          <t>-6,3; 3,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,24; 12,74</t>
+          <t>3,83; 13,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 6,32</t>
+          <t>-1,36; 5,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,58; 10,08</t>
+          <t>4,05; 9,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-56,48; 89,7</t>
+          <t>-55,13; 80,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,87; 883,68</t>
+          <t>44,27; 841,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-27,59; 220,33</t>
+          <t>-26,0; 218,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>81,23; 434,09</t>
+          <t>76,11; 359,73</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>3,18</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>148,7%</t>
+          <t>145,79%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,06</t>
+          <t>2,09; 4,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,78; 5,63</t>
+          <t>3,78; 5,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,69</t>
+          <t>2,09; 3,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,88</t>
+          <t>2,42; 3,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>79,37; 217,92</t>
+          <t>78,61; 215,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>216,49; 535,91</t>
+          <t>219,64; 572,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>127,53; 354,21</t>
+          <t>129,27; 367,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>87,24; 239,65</t>
+          <t>92,95; 213,25</t>
         </is>
       </c>
     </row>
